--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/60.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/60.xlsx
@@ -426,13 +426,13 @@
         <v>-10.34207924108538</v>
       </c>
       <c r="E2">
-        <v>-24.24241330771555</v>
+        <v>-24.38573951005831</v>
       </c>
       <c r="F2">
-        <v>-5.447660624404926</v>
+        <v>-5.571779882570793</v>
       </c>
       <c r="G2">
-        <v>-14.48657268360034</v>
+        <v>-14.56038460694393</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-10.00447827634026</v>
       </c>
       <c r="E3">
-        <v>-23.00443719739466</v>
+        <v>-26.13707249083673</v>
       </c>
       <c r="F3">
-        <v>-4.857058688863559</v>
+        <v>-5.155698391451226</v>
       </c>
       <c r="G3">
-        <v>-14.2719930533814</v>
+        <v>-13.53631865782625</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-9.553502402644524</v>
       </c>
       <c r="E4">
-        <v>-25.32706434508474</v>
+        <v>-26.98540058364164</v>
       </c>
       <c r="F4">
-        <v>-5.324506414263321</v>
+        <v>-4.800146534821622</v>
       </c>
       <c r="G4">
-        <v>-15.56913431712418</v>
+        <v>-14.46680045036704</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-9.013318443229281</v>
       </c>
       <c r="E5">
-        <v>-25.45309630519221</v>
+        <v>-26.5146023119082</v>
       </c>
       <c r="F5">
-        <v>-4.588510260549988</v>
+        <v>-5.40637810651901</v>
       </c>
       <c r="G5">
-        <v>-14.46211933897451</v>
+        <v>-13.66081834392162</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-8.396044935489225</v>
       </c>
       <c r="E6">
-        <v>-24.65011635110012</v>
+        <v>-24.99169914549869</v>
       </c>
       <c r="F6">
-        <v>-5.510423537412836</v>
+        <v>-5.218695732434129</v>
       </c>
       <c r="G6">
-        <v>-13.32536738551835</v>
+        <v>-14.72274369182641</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-7.721733029648673</v>
       </c>
       <c r="E7">
-        <v>-24.58472971490337</v>
+        <v>-26.08066581859719</v>
       </c>
       <c r="F7">
-        <v>-5.115426481796725</v>
+        <v>-4.760566311948459</v>
       </c>
       <c r="G7">
-        <v>-13.42628274519195</v>
+        <v>-16.05345223206463</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-7.007123396737614</v>
       </c>
       <c r="E8">
-        <v>-24.72642566660337</v>
+        <v>-24.14038678832274</v>
       </c>
       <c r="F8">
-        <v>-4.698038655282944</v>
+        <v>-5.032382649666075</v>
       </c>
       <c r="G8">
-        <v>-14.15006069535173</v>
+        <v>-14.33315538221944</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-6.270616973810734</v>
       </c>
       <c r="E9">
-        <v>-26.47545818258589</v>
+        <v>-26.79213889841629</v>
       </c>
       <c r="F9">
-        <v>-4.687417328444249</v>
+        <v>-4.540603288543884</v>
       </c>
       <c r="G9">
-        <v>-14.18750627594643</v>
+        <v>-13.20857795998394</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-5.527243130459724</v>
       </c>
       <c r="E10">
-        <v>-25.2524169795423</v>
+        <v>-25.48609982376011</v>
       </c>
       <c r="F10">
-        <v>-4.817528168034564</v>
+        <v>-4.939839928527523</v>
       </c>
       <c r="G10">
-        <v>-14.63728195873012</v>
+        <v>-14.98848283753648</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-4.790827067641426</v>
       </c>
       <c r="E11">
-        <v>-25.29690470819365</v>
+        <v>-26.46978400465428</v>
       </c>
       <c r="F11">
-        <v>-4.872968313201727</v>
+        <v>-5.07938752957053</v>
       </c>
       <c r="G11">
-        <v>-13.45233011749494</v>
+        <v>-14.17738428296011</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-4.072767037347084</v>
       </c>
       <c r="E12">
-        <v>-26.05321420916269</v>
+        <v>-27.25953628616997</v>
       </c>
       <c r="F12">
-        <v>-4.684132851692149</v>
+        <v>-4.083814166515944</v>
       </c>
       <c r="G12">
-        <v>-13.40525747047204</v>
+        <v>-14.70784458162692</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-3.380839498631595</v>
       </c>
       <c r="E13">
-        <v>-26.05491238691557</v>
+        <v>-28.14364385210948</v>
       </c>
       <c r="F13">
-        <v>-3.904963845679712</v>
+        <v>-3.867509213562132</v>
       </c>
       <c r="G13">
-        <v>-14.25022125064238</v>
+        <v>-13.78853588028116</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.728375583622461</v>
       </c>
       <c r="E14">
-        <v>-23.9865092415421</v>
+        <v>-26.64027199409506</v>
       </c>
       <c r="F14">
-        <v>-4.084451181048697</v>
+        <v>-3.99795802705279</v>
       </c>
       <c r="G14">
-        <v>-11.9135388926586</v>
+        <v>-14.45929709890229</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-2.125030701072443</v>
       </c>
       <c r="E15">
-        <v>-26.36265389505483</v>
+        <v>-27.77256257802494</v>
       </c>
       <c r="F15">
-        <v>-4.466229978018336</v>
+        <v>-4.679483225460236</v>
       </c>
       <c r="G15">
-        <v>-13.38209027278822</v>
+        <v>-13.32404978839372</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.580298123045166</v>
       </c>
       <c r="E16">
-        <v>-26.79139170020503</v>
+        <v>-28.26756554332938</v>
       </c>
       <c r="F16">
-        <v>-3.814527662846478</v>
+        <v>-3.715524504333493</v>
       </c>
       <c r="G16">
-        <v>-14.70009293924672</v>
+        <v>-13.5319222533501</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-1.102984212416796</v>
       </c>
       <c r="E17">
-        <v>-28.34997924179497</v>
+        <v>-30.16464519580766</v>
       </c>
       <c r="F17">
-        <v>-4.325280779329792</v>
+        <v>-3.670752074579582</v>
       </c>
       <c r="G17">
-        <v>-12.1901084881004</v>
+        <v>-14.08364784128841</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.7003674545269356</v>
       </c>
       <c r="E18">
-        <v>-26.74263362056444</v>
+        <v>-30.27313837608343</v>
       </c>
       <c r="F18">
-        <v>-4.523873580476946</v>
+        <v>-3.590252158742929</v>
       </c>
       <c r="G18">
-        <v>-12.23253312918616</v>
+        <v>-13.80505219197659</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.3776195290702034</v>
       </c>
       <c r="E19">
-        <v>-27.24935174812672</v>
+        <v>-27.80787108986274</v>
       </c>
       <c r="F19">
-        <v>-3.319241822508237</v>
+        <v>-3.016403953923183</v>
       </c>
       <c r="G19">
-        <v>-12.51428041785137</v>
+        <v>-13.06573123050993</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-0.1374181091378877</v>
       </c>
       <c r="E20">
-        <v>-28.44500474037192</v>
+        <v>-26.61797831655529</v>
       </c>
       <c r="F20">
-        <v>-3.669522777353828</v>
+        <v>-3.893968925142354</v>
       </c>
       <c r="G20">
-        <v>-12.27359382550974</v>
+        <v>-13.99191262439521</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>0.01989259176944221</v>
       </c>
       <c r="E21">
-        <v>-27.65773406261244</v>
+        <v>-30.65683597875334</v>
       </c>
       <c r="F21">
-        <v>-3.380143393962057</v>
+        <v>-3.231168971875191</v>
       </c>
       <c r="G21">
-        <v>-12.53345840816037</v>
+        <v>-12.88556472117171</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>0.09652397165766052</v>
       </c>
       <c r="E22">
-        <v>-28.09136261969092</v>
+        <v>-28.54858905482338</v>
       </c>
       <c r="F22">
-        <v>-3.250232190915816</v>
+        <v>-2.689438227996787</v>
       </c>
       <c r="G22">
-        <v>-12.24194169960876</v>
+        <v>-13.71593561660495</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>0.09805196841901495</v>
       </c>
       <c r="E23">
-        <v>-27.23176768355493</v>
+        <v>-29.2896557122826</v>
       </c>
       <c r="F23">
-        <v>-3.252655165569005</v>
+        <v>-3.580207375616582</v>
       </c>
       <c r="G23">
-        <v>-11.8593849887272</v>
+        <v>-12.2342314390478</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>0.0293161049153536</v>
       </c>
       <c r="E24">
-        <v>-28.44332467651508</v>
+        <v>-30.81629486974843</v>
       </c>
       <c r="F24">
-        <v>-2.92142003404858</v>
+        <v>-2.993299130324299</v>
       </c>
       <c r="G24">
-        <v>-12.40025198729671</v>
+        <v>-12.92890307282631</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-0.102068873670919</v>
       </c>
       <c r="E25">
-        <v>-27.58168287012763</v>
+        <v>-29.54556204269306</v>
       </c>
       <c r="F25">
-        <v>-3.188387108990208</v>
+        <v>-3.273140691440236</v>
       </c>
       <c r="G25">
-        <v>-12.22828238871373</v>
+        <v>-13.46006355187468</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-0.2870829598837846</v>
       </c>
       <c r="E26">
-        <v>-27.84252297296944</v>
+        <v>-28.32812482623395</v>
       </c>
       <c r="F26">
-        <v>-3.2686915301198</v>
+        <v>-3.452531107823094</v>
       </c>
       <c r="G26">
-        <v>-12.38273258030289</v>
+        <v>-13.4939585723785</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-0.5159388035123491</v>
       </c>
       <c r="E27">
-        <v>-27.99020103883358</v>
+        <v>-29.03125645693092</v>
       </c>
       <c r="F27">
-        <v>-3.569060863844512</v>
+        <v>-3.778718168390859</v>
       </c>
       <c r="G27">
-        <v>-12.51761082666388</v>
+        <v>-13.8043371141401</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-0.7782460353425318</v>
       </c>
       <c r="E28">
-        <v>-28.04048974268876</v>
+        <v>-27.88564310247047</v>
       </c>
       <c r="F28">
-        <v>-3.707421414399308</v>
+        <v>-3.328488059458285</v>
       </c>
       <c r="G28">
-        <v>-11.9982855479184</v>
+        <v>-13.4570641976161</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-1.063168010293381</v>
       </c>
       <c r="E29">
-        <v>-27.23646371110089</v>
+        <v>-28.22674587862424</v>
       </c>
       <c r="F29">
-        <v>-3.099557958918405</v>
+        <v>-2.904992680083663</v>
       </c>
       <c r="G29">
-        <v>-12.93717281558341</v>
+        <v>-14.84527856914422</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-1.360059907408316</v>
       </c>
       <c r="E30">
-        <v>-26.87482883379635</v>
+        <v>-29.59658888781149</v>
       </c>
       <c r="F30">
-        <v>-3.121046637714427</v>
+        <v>-3.101662012121516</v>
       </c>
       <c r="G30">
-        <v>-12.62349531519193</v>
+        <v>-14.06281292293701</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-1.658783967188139</v>
       </c>
       <c r="E31">
-        <v>-26.25957224121823</v>
+        <v>-27.90476684820486</v>
       </c>
       <c r="F31">
-        <v>-3.175673326092041</v>
+        <v>-3.039377067105022</v>
       </c>
       <c r="G31">
-        <v>-12.48329371160379</v>
+        <v>-14.99978172946201</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-1.950670216912295</v>
       </c>
       <c r="E32">
-        <v>-25.05907378178481</v>
+        <v>-28.23704815699169</v>
       </c>
       <c r="F32">
-        <v>-3.476267147382912</v>
+        <v>-3.166591105887747</v>
       </c>
       <c r="G32">
-        <v>-13.81498713913994</v>
+        <v>-14.21906405129953</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-2.227583648406403</v>
       </c>
       <c r="E33">
-        <v>-26.69264832446777</v>
+        <v>-28.85479993874804</v>
       </c>
       <c r="F33">
-        <v>-3.124983867979934</v>
+        <v>-3.357766705310234</v>
       </c>
       <c r="G33">
-        <v>-12.9214079977254</v>
+        <v>-12.37593603031076</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-2.483772282899496</v>
       </c>
       <c r="E34">
-        <v>-25.58631495354986</v>
+        <v>-26.95442582142917</v>
       </c>
       <c r="F34">
-        <v>-3.728235802129451</v>
+        <v>-3.83719676519149</v>
       </c>
       <c r="G34">
-        <v>-12.82724615095191</v>
+        <v>-13.30494131954105</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-2.715366241028064</v>
       </c>
       <c r="E35">
-        <v>-23.60474076879946</v>
+        <v>-25.98468934047863</v>
       </c>
       <c r="F35">
-        <v>-3.453916138120575</v>
+        <v>-3.845677590661351</v>
       </c>
       <c r="G35">
-        <v>-14.00055149297994</v>
+        <v>-13.49129027267385</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-2.919447633372612</v>
       </c>
       <c r="E36">
-        <v>-25.43817951181094</v>
+        <v>-26.34364788964463</v>
       </c>
       <c r="F36">
-        <v>-3.314530897088516</v>
+        <v>-3.279167892663005</v>
       </c>
       <c r="G36">
-        <v>-13.54880769087315</v>
+        <v>-14.37098664136946</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.094262956913774</v>
       </c>
       <c r="E37">
-        <v>-23.88308342368092</v>
+        <v>-26.23163608506491</v>
       </c>
       <c r="F37">
-        <v>-3.135757614420744</v>
+        <v>-3.55532156210168</v>
       </c>
       <c r="G37">
-        <v>-13.16072071366824</v>
+        <v>-14.49669467658666</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-3.239045799925224</v>
       </c>
       <c r="E38">
-        <v>-25.59546699951936</v>
+        <v>-26.52941042191328</v>
       </c>
       <c r="F38">
-        <v>-3.579258066572974</v>
+        <v>-3.293150734422261</v>
       </c>
       <c r="G38">
-        <v>-12.94687933510455</v>
+        <v>-13.88696833080031</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-3.353914347176927</v>
       </c>
       <c r="E39">
-        <v>-23.95726435640056</v>
+        <v>-24.1312754986193</v>
       </c>
       <c r="F39">
-        <v>-3.57632150413005</v>
+        <v>-2.852755831663127</v>
       </c>
       <c r="G39">
-        <v>-13.31803121660333</v>
+        <v>-13.16403125920751</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-3.439627636370428</v>
       </c>
       <c r="E40">
-        <v>-24.2325819906449</v>
+        <v>-25.67866865246229</v>
       </c>
       <c r="F40">
-        <v>-3.482563568011591</v>
+        <v>-2.907080165938718</v>
       </c>
       <c r="G40">
-        <v>-13.0415774902554</v>
+        <v>-14.03725716664661</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-3.497897922266344</v>
       </c>
       <c r="E41">
-        <v>-22.66972409806572</v>
+        <v>-24.62079448190045</v>
       </c>
       <c r="F41">
-        <v>-3.197361641432138</v>
+        <v>-3.652451781916935</v>
       </c>
       <c r="G41">
-        <v>-11.72360958452508</v>
+        <v>-14.5176206349404</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-3.530892204880586</v>
       </c>
       <c r="E42">
-        <v>-24.9979574965773</v>
+        <v>-25.54025131594383</v>
       </c>
       <c r="F42">
-        <v>-2.874619760892617</v>
+        <v>-4.234255627273169</v>
       </c>
       <c r="G42">
-        <v>-11.73039951342612</v>
+        <v>-12.63038787100469</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-3.540785181665032</v>
       </c>
       <c r="E43">
-        <v>-23.03428889805322</v>
+        <v>-26.67588391369138</v>
       </c>
       <c r="F43">
-        <v>-3.270713574950034</v>
+        <v>-3.00336296590091</v>
       </c>
       <c r="G43">
-        <v>-12.93906644763187</v>
+        <v>-11.43756189720435</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-3.531034208878114</v>
       </c>
       <c r="E44">
-        <v>-23.74836585042673</v>
+        <v>-23.77397889941411</v>
       </c>
       <c r="F44">
-        <v>-3.550356327889299</v>
+        <v>-3.935357474055828</v>
       </c>
       <c r="G44">
-        <v>-11.46345036332145</v>
+        <v>-12.85334980252906</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-3.506240214833471</v>
       </c>
       <c r="E45">
-        <v>-21.18997728894931</v>
+        <v>-22.62239248773755</v>
       </c>
       <c r="F45">
-        <v>-3.746738216438381</v>
+        <v>-3.271788795838868</v>
       </c>
       <c r="G45">
-        <v>-12.04505693529723</v>
+        <v>-12.34406871894974</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-3.470791578865302</v>
       </c>
       <c r="E46">
-        <v>-22.75971393354614</v>
+        <v>-25.98237981873471</v>
       </c>
       <c r="F46">
-        <v>-3.336179450793279</v>
+        <v>-3.60930543737472</v>
       </c>
       <c r="G46">
-        <v>-12.92545679491993</v>
+        <v>-13.44177940886128</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.429321221852212</v>
       </c>
       <c r="E47">
-        <v>-20.56293307852922</v>
+        <v>-25.15959231933307</v>
       </c>
       <c r="F47">
-        <v>-3.600898336603708</v>
+        <v>-2.798100150426415</v>
       </c>
       <c r="G47">
-        <v>-11.14027490777779</v>
+        <v>-12.49439397079697</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.386162170819318</v>
       </c>
       <c r="E48">
-        <v>-21.74218393791865</v>
+        <v>-23.77014781040362</v>
       </c>
       <c r="F48">
-        <v>-3.413922559913415</v>
+        <v>-3.511985521424223</v>
       </c>
       <c r="G48">
-        <v>-10.18851292851056</v>
+        <v>-13.67526225410946</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.344935334488505</v>
       </c>
       <c r="E49">
-        <v>-20.95241354250693</v>
+        <v>-22.94941623820146</v>
       </c>
       <c r="F49">
-        <v>-4.014070601404643</v>
+        <v>-3.585196632483644</v>
       </c>
       <c r="G49">
-        <v>-11.37003338929429</v>
+        <v>-12.78043834757215</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.30825971018647</v>
       </c>
       <c r="E50">
-        <v>-21.64336357812326</v>
+        <v>-23.41830349390367</v>
       </c>
       <c r="F50">
-        <v>-3.990717267584919</v>
+        <v>-3.708207535064564</v>
       </c>
       <c r="G50">
-        <v>-11.87455390838814</v>
+        <v>-11.30161765517972</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.27772311900923</v>
       </c>
       <c r="E51">
-        <v>-19.7386828820231</v>
+        <v>-23.85539180512401</v>
       </c>
       <c r="F51">
-        <v>-4.183235650567344</v>
+        <v>-3.595484955626413</v>
       </c>
       <c r="G51">
-        <v>-10.28370104440123</v>
+        <v>-13.15961168091258</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-3.254028103446667</v>
       </c>
       <c r="E52">
-        <v>-21.36197326023464</v>
+        <v>-23.0583079241899</v>
       </c>
       <c r="F52">
-        <v>-4.121571981102949</v>
+        <v>-4.022862064650554</v>
       </c>
       <c r="G52">
-        <v>-11.51351905405738</v>
+        <v>-12.71346270076716</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.235924809396396</v>
       </c>
       <c r="E53">
-        <v>-21.28354914736981</v>
+        <v>-22.29590309720654</v>
       </c>
       <c r="F53">
-        <v>-4.536942732990913</v>
+        <v>-3.726698352229855</v>
       </c>
       <c r="G53">
-        <v>-12.21829447282175</v>
+        <v>-13.46243721302633</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.22281516759671</v>
       </c>
       <c r="E54">
-        <v>-20.38983215958602</v>
+        <v>-22.34821602894315</v>
       </c>
       <c r="F54">
-        <v>-4.067878034420888</v>
+        <v>-2.802595700321408</v>
       </c>
       <c r="G54">
-        <v>-10.95059389055971</v>
+        <v>-12.57196005278209</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.214379665671822</v>
       </c>
       <c r="E55">
-        <v>-20.83497662606601</v>
+        <v>-25.40021731420465</v>
       </c>
       <c r="F55">
-        <v>-3.896803598394734</v>
+        <v>-3.511327797706401</v>
       </c>
       <c r="G55">
-        <v>-11.87875499067748</v>
+        <v>-12.76210454637567</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.208955059329352</v>
       </c>
       <c r="E56">
-        <v>-20.34570670885528</v>
+        <v>-23.01944456025608</v>
       </c>
       <c r="F56">
-        <v>-4.28445220678061</v>
+        <v>-3.505952521629634</v>
       </c>
       <c r="G56">
-        <v>-11.54583328906621</v>
+        <v>-13.2824461626017</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.20469065195706</v>
       </c>
       <c r="E57">
-        <v>-20.34903966572493</v>
+        <v>-21.8973702136875</v>
       </c>
       <c r="F57">
-        <v>-4.34518810475387</v>
+        <v>-3.914487585709697</v>
       </c>
       <c r="G57">
-        <v>-12.18365623484436</v>
+        <v>-12.85656103170216</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.199688909778907</v>
       </c>
       <c r="E58">
-        <v>-20.8034448615506</v>
+        <v>-20.87770730680239</v>
       </c>
       <c r="F58">
-        <v>-4.081463259826799</v>
+        <v>-3.628468888871084</v>
       </c>
       <c r="G58">
-        <v>-12.72120937732905</v>
+        <v>-12.3489881896211</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.192014800348563</v>
       </c>
       <c r="E59">
-        <v>-20.5331085487147</v>
+        <v>-22.78520018526131</v>
       </c>
       <c r="F59">
-        <v>-4.652213370560076</v>
+        <v>-4.327236554767802</v>
       </c>
       <c r="G59">
-        <v>-10.49059689842352</v>
+        <v>-13.11083079239142</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-3.180026047670207</v>
       </c>
       <c r="E60">
-        <v>-19.93710702761719</v>
+        <v>-21.50701575422632</v>
       </c>
       <c r="F60">
-        <v>-4.293765541490285</v>
+        <v>-3.443172212906266</v>
       </c>
       <c r="G60">
-        <v>-10.71992500901991</v>
+        <v>-13.57330738313652</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-3.162859397497413</v>
       </c>
       <c r="E61">
-        <v>-21.44823616160675</v>
+        <v>-21.51147177264986</v>
       </c>
       <c r="F61">
-        <v>-4.711170763719525</v>
+        <v>-3.84251405555006</v>
       </c>
       <c r="G61">
-        <v>-12.02840158068915</v>
+        <v>-13.5612288577365</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-3.140403963479117</v>
       </c>
       <c r="E62">
-        <v>-22.03136323110046</v>
+        <v>-22.30178105646849</v>
       </c>
       <c r="F62">
-        <v>-4.345281710270386</v>
+        <v>-3.973344746413408</v>
       </c>
       <c r="G62">
-        <v>-11.6472617832984</v>
+        <v>-12.81362325605781</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-3.113068506521212</v>
       </c>
       <c r="E63">
-        <v>-21.84584070795422</v>
+        <v>-22.58529522866671</v>
       </c>
       <c r="F63">
-        <v>-4.519189162814114</v>
+        <v>-4.103820067660956</v>
       </c>
       <c r="G63">
-        <v>-11.54202947224159</v>
+        <v>-12.77214874154182</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-3.082544150016698</v>
       </c>
       <c r="E64">
-        <v>-22.02430786859651</v>
+        <v>-21.76290170650374</v>
       </c>
       <c r="F64">
-        <v>-4.443448217706544</v>
+        <v>-4.275221708811215</v>
       </c>
       <c r="G64">
-        <v>-10.58904590167037</v>
+        <v>-12.78415277966722</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-3.053048763432968</v>
       </c>
       <c r="E65">
-        <v>-22.36210938719868</v>
+        <v>-22.08923260044448</v>
       </c>
       <c r="F65">
-        <v>-4.522832322651626</v>
+        <v>-4.308497227381671</v>
       </c>
       <c r="G65">
-        <v>-11.89272880339874</v>
+        <v>-12.83223183253405</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-3.028532739612446</v>
       </c>
       <c r="E66">
-        <v>-21.63013137707285</v>
+        <v>-21.75475045328993</v>
       </c>
       <c r="F66">
-        <v>-4.234775013634724</v>
+        <v>-4.249511669730527</v>
       </c>
       <c r="G66">
-        <v>-11.91170485042985</v>
+        <v>-12.62263788389726</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-3.013205588390382</v>
       </c>
       <c r="E67">
-        <v>-21.67718675048655</v>
+        <v>-24.23818824146639</v>
       </c>
       <c r="F67">
-        <v>-4.826743755390709</v>
+        <v>-4.384760043953005</v>
       </c>
       <c r="G67">
-        <v>-12.22010534123173</v>
+        <v>-13.055958500078</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-3.0115618357588</v>
       </c>
       <c r="E68">
-        <v>-21.69501988112876</v>
+        <v>-22.87973208017143</v>
       </c>
       <c r="F68">
-        <v>-4.035143439764459</v>
+        <v>-3.950983796742238</v>
       </c>
       <c r="G68">
-        <v>-10.28192990253772</v>
+        <v>-13.69898893398942</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-3.028180189194741</v>
       </c>
       <c r="E69">
-        <v>-22.82922148108987</v>
+        <v>-22.75918863056125</v>
       </c>
       <c r="F69">
-        <v>-4.371128429972536</v>
+        <v>-4.41700258837217</v>
       </c>
       <c r="G69">
-        <v>-11.47221668790944</v>
+        <v>-12.37485348191942</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.066847143632776</v>
       </c>
       <c r="E70">
-        <v>-22.09703063268569</v>
+        <v>-22.88995737448075</v>
       </c>
       <c r="F70">
-        <v>-4.790460434780688</v>
+        <v>-3.702841371029229</v>
       </c>
       <c r="G70">
-        <v>-11.68646857411999</v>
+        <v>-11.44681487198661</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.130005130781718</v>
       </c>
       <c r="E71">
-        <v>-22.12287010537345</v>
+        <v>-23.90712509218763</v>
       </c>
       <c r="F71">
-        <v>-4.892980012918557</v>
+        <v>-4.954459784819531</v>
       </c>
       <c r="G71">
-        <v>-9.462351385562508</v>
+        <v>-12.93327961402923</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.21834044675879</v>
       </c>
       <c r="E72">
-        <v>-20.94822470404983</v>
+        <v>-22.23084251113834</v>
       </c>
       <c r="F72">
-        <v>-4.830743941578828</v>
+        <v>-3.830931822524117</v>
       </c>
       <c r="G72">
-        <v>-11.28139684302585</v>
+        <v>-13.96344193275748</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.329788917902007</v>
       </c>
       <c r="E73">
-        <v>-23.27565203418804</v>
+        <v>-23.05985213382652</v>
       </c>
       <c r="F73">
-        <v>-4.630511801341534</v>
+        <v>-4.601562017348497</v>
       </c>
       <c r="G73">
-        <v>-12.65578968692752</v>
+        <v>-12.64607654631529</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.459992788694514</v>
       </c>
       <c r="E74">
-        <v>-23.27065712735758</v>
+        <v>-24.24534323039851</v>
       </c>
       <c r="F74">
-        <v>-4.875252122131245</v>
+        <v>-4.352396557893031</v>
       </c>
       <c r="G74">
-        <v>-11.69787671404832</v>
+        <v>-13.24890040465226</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.605163841703075</v>
       </c>
       <c r="E75">
-        <v>-23.26415423868257</v>
+        <v>-24.76051601893311</v>
       </c>
       <c r="F75">
-        <v>-4.563211091701088</v>
+        <v>-4.360328175774836</v>
       </c>
       <c r="G75">
-        <v>-11.96614346127762</v>
+        <v>-13.0671282807275</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-3.758410546796434</v>
       </c>
       <c r="E76">
-        <v>-23.10882758021948</v>
+        <v>-25.87630484357905</v>
       </c>
       <c r="F76">
-        <v>-4.708789207436476</v>
+        <v>-4.056295801394945</v>
       </c>
       <c r="G76">
-        <v>-11.88572368903765</v>
+        <v>-11.16779216230022</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-3.911785027705351</v>
       </c>
       <c r="E77">
-        <v>-22.93286919417744</v>
+        <v>-23.31151301985479</v>
       </c>
       <c r="F77">
-        <v>-4.972895929736237</v>
+        <v>-4.727015775400274</v>
       </c>
       <c r="G77">
-        <v>-11.24230261075259</v>
+        <v>-12.63452605292878</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.056916051458193</v>
       </c>
       <c r="E78">
-        <v>-24.20263066355816</v>
+        <v>-24.40850867736888</v>
       </c>
       <c r="F78">
-        <v>-5.161241826110761</v>
+        <v>-5.43698876715466</v>
       </c>
       <c r="G78">
-        <v>-11.2222903629677</v>
+        <v>-13.05104233995218</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.185503347223748</v>
       </c>
       <c r="E79">
-        <v>-22.45814926395335</v>
+        <v>-24.21893769845979</v>
       </c>
       <c r="F79">
-        <v>-5.128682016976323</v>
+        <v>-4.765409776152628</v>
       </c>
       <c r="G79">
-        <v>-12.70909609120086</v>
+        <v>-13.52745136159931</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.289912707199149</v>
       </c>
       <c r="E80">
-        <v>-23.2820054832208</v>
+        <v>-25.70823505925837</v>
       </c>
       <c r="F80">
-        <v>-5.688065270208384</v>
+        <v>-4.516767016528329</v>
       </c>
       <c r="G80">
-        <v>-12.35856228732067</v>
+        <v>-13.70707163092355</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.364195207278364</v>
       </c>
       <c r="E81">
-        <v>-25.39553487208071</v>
+        <v>-25.41834026718334</v>
       </c>
       <c r="F81">
-        <v>-4.709397229110131</v>
+        <v>-5.075488404205553</v>
       </c>
       <c r="G81">
-        <v>-12.16210127283816</v>
+        <v>-13.07786106936582</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.404158588736851</v>
       </c>
       <c r="E82">
-        <v>-26.08077903044738</v>
+        <v>-27.50638793280209</v>
       </c>
       <c r="F82">
-        <v>-4.621374080521253</v>
+        <v>-5.112592636911748</v>
       </c>
       <c r="G82">
-        <v>-11.09609898810176</v>
+        <v>-13.04700347439427</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.407633046110637</v>
       </c>
       <c r="E83">
-        <v>-24.69677774727515</v>
+        <v>-26.88128190925728</v>
       </c>
       <c r="F83">
-        <v>-5.268278491696096</v>
+        <v>-4.95744190746961</v>
       </c>
       <c r="G83">
-        <v>-12.06256972119997</v>
+        <v>-13.43187756715332</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.373990899562824</v>
       </c>
       <c r="E84">
-        <v>-26.37135309362356</v>
+        <v>-26.3310542034293</v>
       </c>
       <c r="F84">
-        <v>-5.313172691458218</v>
+        <v>-5.592279490687872</v>
       </c>
       <c r="G84">
-        <v>-13.01554998122566</v>
+        <v>-12.61858577615719</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-4.307342268509784</v>
       </c>
       <c r="E85">
-        <v>-26.97428770842681</v>
+        <v>-26.18943070731342</v>
       </c>
       <c r="F85">
-        <v>-5.427318406094378</v>
+        <v>-4.995865729448465</v>
       </c>
       <c r="G85">
-        <v>-13.16828531022547</v>
+        <v>-13.51192159247459</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-4.211979480303246</v>
       </c>
       <c r="E86">
-        <v>-25.88687430191295</v>
+        <v>-29.62826556349514</v>
       </c>
       <c r="F86">
-        <v>-5.918711748006865</v>
+        <v>-5.736837886150414</v>
       </c>
       <c r="G86">
-        <v>-13.59284953345484</v>
+        <v>-12.14849493067176</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-4.093404810206224</v>
       </c>
       <c r="E87">
-        <v>-27.72976849865245</v>
+        <v>-29.97743808033057</v>
       </c>
       <c r="F87">
-        <v>-5.189425370256208</v>
+        <v>-5.314936285658778</v>
       </c>
       <c r="G87">
-        <v>-12.83300981073578</v>
+        <v>-14.25242110815323</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.958175478717742</v>
       </c>
       <c r="E88">
-        <v>-27.71830693093904</v>
+        <v>-30.62007835523308</v>
       </c>
       <c r="F88">
-        <v>-5.242216396469218</v>
+        <v>-5.41885331960517</v>
       </c>
       <c r="G88">
-        <v>-12.48848795755491</v>
+        <v>-12.86019932124982</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.813463289500769</v>
       </c>
       <c r="E89">
-        <v>-30.22051071540329</v>
+        <v>-29.55021504973594</v>
       </c>
       <c r="F89">
-        <v>-5.973776642740559</v>
+        <v>-6.107234915005588</v>
       </c>
       <c r="G89">
-        <v>-13.17730323627445</v>
+        <v>-13.20364855767597</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.666487069862214</v>
       </c>
       <c r="E90">
-        <v>-30.53551816008785</v>
+        <v>-31.43892381801104</v>
       </c>
       <c r="F90">
-        <v>-5.881991877775569</v>
+        <v>-5.745362615092624</v>
       </c>
       <c r="G90">
-        <v>-13.84002148450791</v>
+        <v>-13.31669375620546</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.52430950426396</v>
       </c>
       <c r="E91">
-        <v>-33.1229749962205</v>
+        <v>-31.02229968083136</v>
       </c>
       <c r="F91">
-        <v>-5.393915318943892</v>
+        <v>-5.31483025463122</v>
       </c>
       <c r="G91">
-        <v>-12.91423073499626</v>
+        <v>-14.40402588585138</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.393766658173267</v>
       </c>
       <c r="E92">
-        <v>-32.09241884510994</v>
+        <v>-33.80133360985851</v>
       </c>
       <c r="F92">
-        <v>-6.362355507719779</v>
+        <v>-5.526407714817256</v>
       </c>
       <c r="G92">
-        <v>-12.73669279881623</v>
+        <v>-14.74635284733972</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-3.281072219333436</v>
       </c>
       <c r="E93">
-        <v>-33.54343475088468</v>
+        <v>-33.41007798406979</v>
       </c>
       <c r="F93">
-        <v>-6.213762134638201</v>
+        <v>-6.142905243737538</v>
       </c>
       <c r="G93">
-        <v>-12.96554088030942</v>
+        <v>-14.33254789711298</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-3.190757876266495</v>
       </c>
       <c r="E94">
-        <v>-35.67461386718948</v>
+        <v>-33.86272160350649</v>
       </c>
       <c r="F94">
-        <v>-6.269609836567541</v>
+        <v>-5.808210849943023</v>
       </c>
       <c r="G94">
-        <v>-14.12905362863229</v>
+        <v>-13.89158323128206</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.130340026300462</v>
       </c>
       <c r="E95">
-        <v>-36.59506922975155</v>
+        <v>-37.0004582229182</v>
       </c>
       <c r="F95">
-        <v>-6.704658870292709</v>
+        <v>-6.298630445973518</v>
       </c>
       <c r="G95">
-        <v>-13.52027409887017</v>
+        <v>-14.17276441666005</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.105802143167427</v>
       </c>
       <c r="E96">
-        <v>-36.50372311630584</v>
+        <v>-39.93219908819501</v>
       </c>
       <c r="F96">
-        <v>-6.392770673648369</v>
+        <v>-6.979569160259781</v>
       </c>
       <c r="G96">
-        <v>-14.3547119994984</v>
+        <v>-16.16434226544805</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.118754762886302</v>
       </c>
       <c r="E97">
-        <v>-38.42483538034282</v>
+        <v>-41.09077293526541</v>
       </c>
       <c r="F97">
-        <v>-6.248667051889964</v>
+        <v>-6.526757030132682</v>
       </c>
       <c r="G97">
-        <v>-13.74584805082503</v>
+        <v>-14.03096216430368</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-3.174621441583698</v>
       </c>
       <c r="E98">
-        <v>-40.64349555752781</v>
+        <v>-42.53736905040866</v>
       </c>
       <c r="F98">
-        <v>-6.257662707700665</v>
+        <v>-6.742865660012031</v>
       </c>
       <c r="G98">
-        <v>-13.46825053099329</v>
+        <v>-13.76678063026984</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-3.269043557142948</v>
       </c>
       <c r="E99">
-        <v>-43.62682479869999</v>
+        <v>-41.09479874865822</v>
       </c>
       <c r="F99">
-        <v>-6.4540011069611</v>
+        <v>-7.266254278673947</v>
       </c>
       <c r="G99">
-        <v>-13.64624863300329</v>
+        <v>-15.24458995100003</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-3.409604018647338</v>
       </c>
       <c r="E100">
-        <v>-45.03226840629853</v>
+        <v>-45.83978362710931</v>
       </c>
       <c r="F100">
-        <v>-6.681097202071181</v>
+        <v>-7.733121318524345</v>
       </c>
       <c r="G100">
-        <v>-14.76679712131749</v>
+        <v>-14.66103015715608</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-3.58212383930213</v>
       </c>
       <c r="E101">
-        <v>-45.47119754220299</v>
+        <v>-46.84769740818152</v>
       </c>
       <c r="F101">
-        <v>-6.981197730573685</v>
+        <v>-8.183186582343762</v>
       </c>
       <c r="G101">
-        <v>-14.35645996754313</v>
+        <v>-16.03183768023872</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-3.805831621275297</v>
       </c>
       <c r="E102">
-        <v>-47.31034216246415</v>
+        <v>-47.97533272083152</v>
       </c>
       <c r="F102">
-        <v>-7.266340014700137</v>
+        <v>-7.661335827765143</v>
       </c>
       <c r="G102">
-        <v>-15.9903433024495</v>
+        <v>-15.66064938273902</v>
       </c>
     </row>
   </sheetData>
